--- a/templates/fomio_template.xlsx
+++ b/templates/fomio_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE44D08-F0EB-4358-ABE1-90156418EF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481530AB-86EB-456E-B722-05699E49D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F24CC36B-B49E-40ED-906B-853EB2E37C31}"/>
   </bookViews>
@@ -1450,6 +1450,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1508,915 +1547,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="208">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="104">
     <dxf>
       <fill>
         <patternFill>
@@ -3444,9 +2581,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3484,7 +2621,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3590,7 +2727,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3732,7 +2869,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3765,80 +2902,80 @@
     </row>
     <row r="5" spans="3:37"/>
     <row r="6" spans="3:37">
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="92"/>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="92"/>
-      <c r="P6" s="92"/>
-      <c r="Q6" s="92"/>
-      <c r="R6" s="92"/>
-      <c r="S6" s="92"/>
-      <c r="T6" s="92"/>
-      <c r="U6" s="92"/>
-      <c r="V6" s="92"/>
-      <c r="W6" s="92"/>
-      <c r="X6" s="92"/>
-      <c r="Y6" s="92"/>
-      <c r="Z6" s="92"/>
-      <c r="AA6" s="92"/>
-      <c r="AB6" s="92"/>
-      <c r="AC6" s="92"/>
-      <c r="AD6" s="92"/>
-      <c r="AE6" s="92"/>
-      <c r="AF6" s="92"/>
-      <c r="AG6" s="92"/>
-      <c r="AH6" s="92"/>
-      <c r="AI6" s="92"/>
-      <c r="AJ6" s="92"/>
-      <c r="AK6" s="92"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="75"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="75"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75"/>
+      <c r="S6" s="75"/>
+      <c r="T6" s="75"/>
+      <c r="U6" s="75"/>
+      <c r="V6" s="75"/>
+      <c r="W6" s="75"/>
+      <c r="X6" s="75"/>
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75"/>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75"/>
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75"/>
+      <c r="AG6" s="75"/>
+      <c r="AH6" s="75"/>
+      <c r="AI6" s="75"/>
+      <c r="AJ6" s="75"/>
+      <c r="AK6" s="75"/>
     </row>
     <row r="7" spans="3:37">
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
-      <c r="Q7" s="92"/>
-      <c r="R7" s="92"/>
-      <c r="S7" s="92"/>
-      <c r="T7" s="92"/>
-      <c r="U7" s="92"/>
-      <c r="V7" s="92"/>
-      <c r="W7" s="92"/>
-      <c r="X7" s="92"/>
-      <c r="Y7" s="92"/>
-      <c r="Z7" s="92"/>
-      <c r="AA7" s="92"/>
-      <c r="AB7" s="92"/>
-      <c r="AC7" s="92"/>
-      <c r="AD7" s="92"/>
-      <c r="AE7" s="92"/>
-      <c r="AF7" s="92"/>
-      <c r="AG7" s="92"/>
-      <c r="AH7" s="92"/>
-      <c r="AI7" s="92"/>
-      <c r="AJ7" s="92"/>
-      <c r="AK7" s="92"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="S7" s="75"/>
+      <c r="T7" s="75"/>
+      <c r="U7" s="75"/>
+      <c r="V7" s="75"/>
+      <c r="W7" s="75"/>
+      <c r="X7" s="75"/>
+      <c r="Y7" s="75"/>
+      <c r="Z7" s="75"/>
+      <c r="AA7" s="75"/>
+      <c r="AB7" s="75"/>
+      <c r="AC7" s="75"/>
+      <c r="AD7" s="75"/>
+      <c r="AE7" s="75"/>
+      <c r="AF7" s="75"/>
+      <c r="AG7" s="75"/>
+      <c r="AH7" s="75"/>
+      <c r="AI7" s="75"/>
+      <c r="AJ7" s="75"/>
+      <c r="AK7" s="75"/>
     </row>
     <row r="8" spans="3:37" s="69" customFormat="1" ht="3.75" customHeight="1">
       <c r="F8" s="69" t="str">
@@ -3867,53 +3004,53 @@
       </c>
     </row>
     <row r="9" spans="3:37" ht="18.75">
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="93"/>
-      <c r="S9" s="93"/>
-      <c r="T9" s="93"/>
-      <c r="U9" s="93"/>
-      <c r="V9" s="93"/>
-      <c r="W9" s="93"/>
-      <c r="X9" s="93"/>
-      <c r="Y9" s="93"/>
-      <c r="Z9" s="93"/>
-      <c r="AA9" s="93"/>
-      <c r="AB9" s="93"/>
-      <c r="AC9" s="93"/>
-      <c r="AD9" s="93"/>
-      <c r="AE9" s="93"/>
-      <c r="AF9" s="93"/>
-      <c r="AG9" s="93"/>
-      <c r="AH9" s="93"/>
-      <c r="AI9" s="93"/>
-      <c r="AJ9" s="93"/>
-      <c r="AK9" s="93"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="76"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="76"/>
     </row>
     <row r="10" spans="3:37" ht="3.75" customHeight="1">
       <c r="F10" s="70"/>
     </row>
     <row r="11" spans="3:37">
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="98" t="s">
+      <c r="E11" s="81" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="61"/>
@@ -3947,14 +3084,14 @@
       <c r="AH11" s="61"/>
       <c r="AI11" s="61"/>
       <c r="AJ11" s="61"/>
-      <c r="AK11" s="100" t="s">
+      <c r="AK11" s="83" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="3:37">
-      <c r="C12" s="95"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="99"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="82"/>
       <c r="F12" s="62"/>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
@@ -3986,51 +3123,51 @@
       <c r="AH12" s="63"/>
       <c r="AI12" s="63"/>
       <c r="AJ12" s="64"/>
-      <c r="AK12" s="101"/>
+      <c r="AK12" s="84"/>
     </row>
     <row r="13" spans="3:37">
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82"/>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
-      <c r="R13" s="82"/>
-      <c r="S13" s="82"/>
-      <c r="T13" s="82"/>
-      <c r="U13" s="82"/>
-      <c r="V13" s="82"/>
-      <c r="W13" s="82"/>
-      <c r="X13" s="82"/>
-      <c r="Y13" s="82"/>
-      <c r="Z13" s="82"/>
-      <c r="AA13" s="82"/>
-      <c r="AB13" s="82"/>
-      <c r="AC13" s="82"/>
-      <c r="AD13" s="82"/>
-      <c r="AE13" s="82"/>
-      <c r="AF13" s="82"/>
-      <c r="AG13" s="82"/>
-      <c r="AH13" s="82"/>
-      <c r="AI13" s="82"/>
-      <c r="AJ13" s="82"/>
-      <c r="AK13" s="83"/>
-    </row>
-    <row r="14" spans="3:37">
-      <c r="C14" s="102"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="104"/>
+      <c r="D13" s="95"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="95"/>
+      <c r="N13" s="95"/>
+      <c r="O13" s="95"/>
+      <c r="P13" s="95"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="95"/>
+      <c r="S13" s="95"/>
+      <c r="T13" s="95"/>
+      <c r="U13" s="95"/>
+      <c r="V13" s="95"/>
+      <c r="W13" s="95"/>
+      <c r="X13" s="95"/>
+      <c r="Y13" s="95"/>
+      <c r="Z13" s="95"/>
+      <c r="AA13" s="95"/>
+      <c r="AB13" s="95"/>
+      <c r="AC13" s="95"/>
+      <c r="AD13" s="95"/>
+      <c r="AE13" s="95"/>
+      <c r="AF13" s="95"/>
+      <c r="AG13" s="95"/>
+      <c r="AH13" s="95"/>
+      <c r="AI13" s="95"/>
+      <c r="AJ13" s="95"/>
+      <c r="AK13" s="96"/>
+    </row>
+    <row r="14" spans="3:37" ht="13.5" customHeight="1">
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="74"/>
       <c r="F14" s="4"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -4067,7 +3204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:37">
+    <row r="15" spans="3:37" ht="13.5" customHeight="1">
       <c r="C15" s="49"/>
       <c r="D15" s="50"/>
       <c r="E15" s="51"/>
@@ -4107,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:37">
+    <row r="16" spans="3:37" ht="13.5" customHeight="1">
       <c r="C16" s="52"/>
       <c r="D16" s="53"/>
       <c r="E16" s="54"/>
@@ -4148,45 +3285,45 @@
       </c>
     </row>
     <row r="17" spans="3:38">
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="82"/>
-      <c r="E17" s="82"/>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="84"/>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="84"/>
-      <c r="M17" s="84"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="84"/>
-      <c r="R17" s="84"/>
-      <c r="S17" s="84"/>
-      <c r="T17" s="84"/>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="84"/>
-      <c r="X17" s="84"/>
-      <c r="Y17" s="84"/>
-      <c r="Z17" s="84"/>
-      <c r="AA17" s="84"/>
-      <c r="AB17" s="84"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
-      <c r="AF17" s="84"/>
-      <c r="AG17" s="84"/>
-      <c r="AH17" s="84"/>
-      <c r="AI17" s="84"/>
-      <c r="AJ17" s="84"/>
-      <c r="AK17" s="83"/>
-    </row>
-    <row r="18" spans="3:38">
+      <c r="D17" s="95"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="97"/>
+      <c r="P17" s="97"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="97"/>
+      <c r="S17" s="97"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="97"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="97"/>
+      <c r="X17" s="97"/>
+      <c r="Y17" s="97"/>
+      <c r="Z17" s="97"/>
+      <c r="AA17" s="97"/>
+      <c r="AB17" s="97"/>
+      <c r="AC17" s="97"/>
+      <c r="AD17" s="97"/>
+      <c r="AE17" s="97"/>
+      <c r="AF17" s="97"/>
+      <c r="AG17" s="97"/>
+      <c r="AH17" s="97"/>
+      <c r="AI17" s="97"/>
+      <c r="AJ17" s="97"/>
+      <c r="AK17" s="96"/>
+    </row>
+    <row r="18" spans="3:38" ht="13.5" customHeight="1">
       <c r="C18" s="55"/>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
@@ -4230,7 +3367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:38">
+    <row r="19" spans="3:38" ht="13.5" customHeight="1">
       <c r="C19" s="58"/>
       <c r="D19" s="59"/>
       <c r="E19" s="60"/>
@@ -4270,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:38">
+    <row r="20" spans="3:38" ht="13.5" customHeight="1">
       <c r="C20" s="58"/>
       <c r="D20" s="59"/>
       <c r="E20" s="60"/>
@@ -4310,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:38">
+    <row r="21" spans="3:38" ht="13.5" customHeight="1">
       <c r="C21" s="58"/>
       <c r="D21" s="59"/>
       <c r="E21" s="60"/>
@@ -4350,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:38">
+    <row r="22" spans="3:38" ht="13.5" customHeight="1">
       <c r="C22" s="58"/>
       <c r="D22" s="59"/>
       <c r="E22" s="60"/>
@@ -4390,7 +3527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:38">
+    <row r="23" spans="3:38" ht="13.5" customHeight="1">
       <c r="C23" s="58"/>
       <c r="D23" s="59"/>
       <c r="E23" s="60"/>
@@ -4430,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:38">
+    <row r="24" spans="3:38" ht="13.5" customHeight="1">
       <c r="C24" s="58"/>
       <c r="D24" s="59"/>
       <c r="E24" s="60"/>
@@ -4470,7 +3607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:38">
+    <row r="25" spans="3:38" ht="13.5" customHeight="1">
       <c r="C25" s="58"/>
       <c r="D25" s="59"/>
       <c r="E25" s="60"/>
@@ -4510,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:38">
+    <row r="26" spans="3:38" ht="13.5" customHeight="1">
       <c r="C26" s="58"/>
       <c r="D26" s="59"/>
       <c r="E26" s="60"/>
@@ -4550,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:38">
+    <row r="27" spans="3:38" ht="13.5" customHeight="1">
       <c r="C27" s="58"/>
       <c r="D27" s="59"/>
       <c r="E27" s="60"/>
@@ -4590,7 +3727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:38">
+    <row r="28" spans="3:38" ht="13.5" customHeight="1">
       <c r="C28" s="58"/>
       <c r="D28" s="59"/>
       <c r="E28" s="60"/>
@@ -4630,7 +3767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:38">
+    <row r="29" spans="3:38" ht="13.5" customHeight="1">
       <c r="C29" s="58"/>
       <c r="D29" s="59"/>
       <c r="E29" s="60"/>
@@ -4670,7 +3807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:38">
+    <row r="30" spans="3:38" ht="13.5" customHeight="1">
       <c r="C30" s="58"/>
       <c r="D30" s="59"/>
       <c r="E30" s="60"/>
@@ -4710,7 +3847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:38">
+    <row r="31" spans="3:38" ht="13.5" customHeight="1">
       <c r="C31" s="58"/>
       <c r="D31" s="59"/>
       <c r="E31" s="60"/>
@@ -4750,7 +3887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:38">
+    <row r="32" spans="3:38" ht="13.5" customHeight="1">
       <c r="C32" s="58"/>
       <c r="D32" s="59"/>
       <c r="E32" s="60"/>
@@ -4790,7 +3927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:37">
+    <row r="33" spans="3:37" ht="13.5" customHeight="1">
       <c r="C33" s="58"/>
       <c r="D33" s="59"/>
       <c r="E33" s="60"/>
@@ -4830,7 +3967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:37">
+    <row r="34" spans="3:37" ht="13.5" customHeight="1">
       <c r="C34" s="58"/>
       <c r="D34" s="59"/>
       <c r="E34" s="60"/>
@@ -4870,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:37">
+    <row r="35" spans="3:37" ht="13.5" customHeight="1">
       <c r="C35" s="58"/>
       <c r="D35" s="59"/>
       <c r="E35" s="60"/>
@@ -4910,7 +4047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:37">
+    <row r="36" spans="3:37" ht="13.5" customHeight="1">
       <c r="C36" s="58"/>
       <c r="D36" s="59"/>
       <c r="E36" s="60"/>
@@ -4950,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:37">
+    <row r="37" spans="3:37" ht="13.5" customHeight="1">
       <c r="C37" s="58"/>
       <c r="D37" s="59"/>
       <c r="E37" s="60"/>
@@ -4990,7 +4127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:37">
+    <row r="38" spans="3:37" ht="13.5" customHeight="1">
       <c r="C38" s="58"/>
       <c r="D38" s="59"/>
       <c r="E38" s="60"/>
@@ -5030,7 +4167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:37">
+    <row r="39" spans="3:37" ht="13.5" customHeight="1">
       <c r="C39" s="58"/>
       <c r="D39" s="59"/>
       <c r="E39" s="60"/>
@@ -5070,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:37">
+    <row r="40" spans="3:37" ht="13.5" customHeight="1">
       <c r="C40" s="58"/>
       <c r="D40" s="59"/>
       <c r="E40" s="60"/>
@@ -5110,7 +4247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:37">
+    <row r="41" spans="3:37" ht="13.5" customHeight="1">
       <c r="C41" s="58"/>
       <c r="D41" s="59"/>
       <c r="E41" s="60"/>
@@ -5150,7 +4287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:37">
+    <row r="42" spans="3:37" ht="13.5" customHeight="1">
       <c r="C42" s="58"/>
       <c r="D42" s="59"/>
       <c r="E42" s="60"/>
@@ -5190,7 +4327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:37">
+    <row r="43" spans="3:37" ht="13.5" customHeight="1">
       <c r="C43" s="58"/>
       <c r="D43" s="59"/>
       <c r="E43" s="60"/>
@@ -5230,7 +4367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:37">
+    <row r="44" spans="3:37" ht="13.5" customHeight="1">
       <c r="C44" s="58"/>
       <c r="D44" s="59"/>
       <c r="E44" s="60"/>
@@ -5270,7 +4407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:37">
+    <row r="45" spans="3:37" ht="13.5" customHeight="1">
       <c r="C45" s="58"/>
       <c r="D45" s="59"/>
       <c r="E45" s="60"/>
@@ -5310,7 +4447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:37">
+    <row r="46" spans="3:37" ht="13.5" customHeight="1">
       <c r="C46" s="58"/>
       <c r="D46" s="59"/>
       <c r="E46" s="60"/>
@@ -5350,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:37">
+    <row r="47" spans="3:37" ht="13.5" customHeight="1">
       <c r="C47" s="58"/>
       <c r="D47" s="59"/>
       <c r="E47" s="60"/>
@@ -5390,7 +4527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:37">
+    <row r="48" spans="3:37" ht="13.5" customHeight="1">
       <c r="C48" s="58"/>
       <c r="D48" s="59"/>
       <c r="E48" s="60"/>
@@ -5430,7 +4567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:37">
+    <row r="49" spans="3:37" ht="13.5" customHeight="1">
       <c r="C49" s="58"/>
       <c r="D49" s="59"/>
       <c r="E49" s="60"/>
@@ -5470,7 +4607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:37">
+    <row r="50" spans="3:37" ht="13.5" customHeight="1">
       <c r="C50" s="58"/>
       <c r="D50" s="59"/>
       <c r="E50" s="60"/>
@@ -5510,7 +4647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:37">
+    <row r="51" spans="3:37" ht="13.5" customHeight="1">
       <c r="C51" s="58"/>
       <c r="D51" s="59"/>
       <c r="E51" s="60"/>
@@ -5550,7 +4687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:37">
+    <row r="52" spans="3:37" ht="13.5" customHeight="1">
       <c r="C52" s="58"/>
       <c r="D52" s="59"/>
       <c r="E52" s="60"/>
@@ -5590,7 +4727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:37">
+    <row r="53" spans="3:37" ht="13.5" customHeight="1">
       <c r="C53" s="58"/>
       <c r="D53" s="59"/>
       <c r="E53" s="60"/>
@@ -5630,7 +4767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:37">
+    <row r="54" spans="3:37" ht="13.5" customHeight="1">
       <c r="C54" s="58"/>
       <c r="D54" s="59"/>
       <c r="E54" s="60"/>
@@ -5670,7 +4807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:37">
+    <row r="55" spans="3:37" ht="13.5" customHeight="1">
       <c r="C55" s="58"/>
       <c r="D55" s="59"/>
       <c r="E55" s="60"/>
@@ -5710,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="3:37">
+    <row r="56" spans="3:37" ht="13.5" customHeight="1">
       <c r="C56" s="58"/>
       <c r="D56" s="59"/>
       <c r="E56" s="60"/>
@@ -5750,7 +4887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:37">
+    <row r="57" spans="3:37" ht="13.5" customHeight="1">
       <c r="C57" s="58"/>
       <c r="D57" s="59"/>
       <c r="E57" s="60"/>
@@ -5790,7 +4927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="3:37">
+    <row r="58" spans="3:37" ht="13.5" customHeight="1">
       <c r="C58" s="58"/>
       <c r="D58" s="59"/>
       <c r="E58" s="60"/>
@@ -5830,7 +4967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="3:37">
+    <row r="59" spans="3:37" ht="13.5" customHeight="1">
       <c r="C59" s="58"/>
       <c r="D59" s="59"/>
       <c r="E59" s="60"/>
@@ -5870,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="3:37">
+    <row r="60" spans="3:37" ht="13.5" customHeight="1">
       <c r="C60" s="58"/>
       <c r="D60" s="59"/>
       <c r="E60" s="60"/>
@@ -5910,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="3:37">
+    <row r="61" spans="3:37" ht="13.5" customHeight="1">
       <c r="C61" s="58"/>
       <c r="D61" s="59"/>
       <c r="E61" s="60"/>
@@ -5950,7 +5087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:37">
+    <row r="62" spans="3:37" ht="13.5" customHeight="1">
       <c r="C62" s="58"/>
       <c r="D62" s="59"/>
       <c r="E62" s="60"/>
@@ -5990,7 +5127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="3:37">
+    <row r="63" spans="3:37" ht="13.5" customHeight="1">
       <c r="C63" s="58"/>
       <c r="D63" s="59"/>
       <c r="E63" s="60"/>
@@ -6030,7 +5167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="3:37">
+    <row r="64" spans="3:37" ht="13.5" customHeight="1">
       <c r="C64" s="58"/>
       <c r="D64" s="59"/>
       <c r="E64" s="60"/>
@@ -6070,7 +5207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="3:37">
+    <row r="65" spans="3:37" ht="13.5" customHeight="1">
       <c r="C65" s="58"/>
       <c r="D65" s="59"/>
       <c r="E65" s="60"/>
@@ -6110,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="3:37">
+    <row r="66" spans="3:37" ht="13.5" customHeight="1">
       <c r="C66" s="58"/>
       <c r="D66" s="59"/>
       <c r="E66" s="60"/>
@@ -6150,7 +5287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="3:37">
+    <row r="67" spans="3:37" ht="13.5" customHeight="1">
       <c r="C67" s="58"/>
       <c r="D67" s="59"/>
       <c r="E67" s="60"/>
@@ -6190,7 +5327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="3:37">
+    <row r="68" spans="3:37" ht="13.5" customHeight="1">
       <c r="C68" s="58"/>
       <c r="D68" s="59"/>
       <c r="E68" s="60"/>
@@ -6230,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="3:37">
+    <row r="69" spans="3:37" ht="13.5" customHeight="1">
       <c r="C69" s="58"/>
       <c r="D69" s="59"/>
       <c r="E69" s="60"/>
@@ -6270,7 +5407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="3:37">
+    <row r="70" spans="3:37" ht="13.5" customHeight="1">
       <c r="C70" s="58"/>
       <c r="D70" s="59"/>
       <c r="E70" s="60"/>
@@ -6310,7 +5447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="3:37">
+    <row r="71" spans="3:37" ht="13.5" customHeight="1">
       <c r="C71" s="58"/>
       <c r="D71" s="59"/>
       <c r="E71" s="60"/>
@@ -6350,7 +5487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="3:37">
+    <row r="72" spans="3:37" ht="13.5" customHeight="1">
       <c r="C72" s="58"/>
       <c r="D72" s="59"/>
       <c r="E72" s="60"/>
@@ -6390,7 +5527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="3:37">
+    <row r="73" spans="3:37" ht="13.5" customHeight="1">
       <c r="C73" s="58"/>
       <c r="D73" s="39"/>
       <c r="E73" s="40"/>
@@ -6430,7 +5567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="3:37">
+    <row r="74" spans="3:37" ht="13.5" customHeight="1">
       <c r="C74" s="58"/>
       <c r="D74" s="39"/>
       <c r="E74" s="40"/>
@@ -6470,7 +5607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="3:37">
+    <row r="75" spans="3:37" ht="13.5" customHeight="1">
       <c r="C75" s="38"/>
       <c r="D75" s="39"/>
       <c r="E75" s="40"/>
@@ -6510,7 +5647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="3:37">
+    <row r="76" spans="3:37" ht="13.5" customHeight="1">
       <c r="C76" s="38"/>
       <c r="D76" s="39"/>
       <c r="E76" s="40"/>
@@ -6550,7 +5687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="3:37">
+    <row r="77" spans="3:37" ht="13.5" customHeight="1">
       <c r="C77" s="38"/>
       <c r="D77" s="39"/>
       <c r="E77" s="40"/>
@@ -6590,7 +5727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="3:37">
+    <row r="78" spans="3:37" ht="13.5" customHeight="1">
       <c r="C78" s="38"/>
       <c r="D78" s="39"/>
       <c r="E78" s="40"/>
@@ -6630,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="3:37">
+    <row r="79" spans="3:37" ht="13.5" customHeight="1">
       <c r="C79" s="38"/>
       <c r="D79" s="39"/>
       <c r="E79" s="40"/>
@@ -6670,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="3:37">
+    <row r="80" spans="3:37" ht="13.5" customHeight="1">
       <c r="C80" s="38"/>
       <c r="D80" s="39"/>
       <c r="E80" s="40"/>
@@ -6710,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="3:37">
+    <row r="81" spans="3:37" ht="13.5" customHeight="1">
       <c r="C81" s="38"/>
       <c r="D81" s="39"/>
       <c r="E81" s="40"/>
@@ -6750,7 +5887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:37">
+    <row r="82" spans="3:37" ht="13.5" customHeight="1">
       <c r="C82" s="38"/>
       <c r="D82" s="39"/>
       <c r="E82" s="40"/>
@@ -6790,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="3:37">
+    <row r="83" spans="3:37" ht="13.5" customHeight="1">
       <c r="C83" s="38"/>
       <c r="D83" s="39"/>
       <c r="E83" s="40"/>
@@ -6830,7 +5967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:37">
+    <row r="84" spans="3:37" ht="13.5" customHeight="1">
       <c r="C84" s="38"/>
       <c r="D84" s="39"/>
       <c r="E84" s="40"/>
@@ -6870,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="3:37">
+    <row r="85" spans="3:37" ht="13.5" customHeight="1">
       <c r="C85" s="38"/>
       <c r="D85" s="39"/>
       <c r="E85" s="40"/>
@@ -6910,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="3:37">
+    <row r="86" spans="3:37" ht="13.5" customHeight="1">
       <c r="C86" s="38"/>
       <c r="D86" s="39"/>
       <c r="E86" s="40"/>
@@ -6950,7 +6087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="3:37">
+    <row r="87" spans="3:37" ht="13.5" customHeight="1">
       <c r="C87" s="38"/>
       <c r="D87" s="39"/>
       <c r="E87" s="40"/>
@@ -6990,7 +6127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="3:37">
+    <row r="88" spans="3:37" ht="13.5" customHeight="1">
       <c r="C88" s="38"/>
       <c r="D88" s="39"/>
       <c r="E88" s="40"/>
@@ -7030,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="3:37">
+    <row r="89" spans="3:37" ht="13.5" customHeight="1">
       <c r="C89" s="38"/>
       <c r="D89" s="39"/>
       <c r="E89" s="40"/>
@@ -7070,7 +6207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:37">
+    <row r="90" spans="3:37" ht="13.5" customHeight="1">
       <c r="C90" s="38"/>
       <c r="D90" s="39"/>
       <c r="E90" s="40"/>
@@ -7110,7 +6247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="3:37">
+    <row r="91" spans="3:37" ht="13.5" customHeight="1">
       <c r="C91" s="38"/>
       <c r="D91" s="39"/>
       <c r="E91" s="40"/>
@@ -7150,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:37">
+    <row r="92" spans="3:37" ht="13.5" customHeight="1">
       <c r="C92" s="38"/>
       <c r="D92" s="39"/>
       <c r="E92" s="40"/>
@@ -7190,7 +6327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="3:37">
+    <row r="93" spans="3:37" ht="13.5" customHeight="1">
       <c r="C93" s="38"/>
       <c r="D93" s="39"/>
       <c r="E93" s="40"/>
@@ -7230,7 +6367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="3:37">
+    <row r="94" spans="3:37" ht="13.5" customHeight="1">
       <c r="C94" s="38"/>
       <c r="D94" s="39"/>
       <c r="E94" s="40"/>
@@ -7270,7 +6407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="3:37">
+    <row r="95" spans="3:37" ht="13.5" customHeight="1">
       <c r="C95" s="38"/>
       <c r="D95" s="39"/>
       <c r="E95" s="40"/>
@@ -7310,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="3:37">
+    <row r="96" spans="3:37" ht="13.5" customHeight="1">
       <c r="C96" s="38"/>
       <c r="D96" s="39"/>
       <c r="E96" s="40"/>
@@ -7350,7 +6487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37">
+    <row r="97" spans="3:37" ht="13.5" customHeight="1">
       <c r="C97" s="38"/>
       <c r="D97" s="39"/>
       <c r="E97" s="40"/>
@@ -7390,7 +6527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="3:37">
+    <row r="98" spans="3:37" ht="13.5" customHeight="1">
       <c r="C98" s="38"/>
       <c r="D98" s="39"/>
       <c r="E98" s="40"/>
@@ -7430,7 +6567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="3:37">
+    <row r="99" spans="3:37" ht="13.5" customHeight="1">
       <c r="C99" s="38"/>
       <c r="D99" s="39"/>
       <c r="E99" s="40"/>
@@ -7470,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="3:37">
+    <row r="100" spans="3:37" ht="13.5" customHeight="1">
       <c r="C100" s="38"/>
       <c r="D100" s="39"/>
       <c r="E100" s="40"/>
@@ -7510,7 +6647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:37">
+    <row r="101" spans="3:37" ht="13.5" customHeight="1">
       <c r="C101" s="38"/>
       <c r="D101" s="39"/>
       <c r="E101" s="40"/>
@@ -7550,7 +6687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:37">
+    <row r="102" spans="3:37" ht="13.5" customHeight="1">
       <c r="C102" s="38"/>
       <c r="D102" s="39"/>
       <c r="E102" s="40"/>
@@ -7590,7 +6727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="3:37">
+    <row r="103" spans="3:37" ht="13.5" customHeight="1">
       <c r="C103" s="38"/>
       <c r="D103" s="39"/>
       <c r="E103" s="40"/>
@@ -7630,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="3:37">
+    <row r="104" spans="3:37" ht="13.5" customHeight="1">
       <c r="C104" s="38"/>
       <c r="D104" s="39"/>
       <c r="E104" s="40"/>
@@ -7670,7 +6807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="3:37">
+    <row r="105" spans="3:37" ht="13.5" customHeight="1">
       <c r="C105" s="38"/>
       <c r="D105" s="39"/>
       <c r="E105" s="40"/>
@@ -7710,7 +6847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="3:37">
+    <row r="106" spans="3:37" ht="13.5" customHeight="1">
       <c r="C106" s="38"/>
       <c r="D106" s="39"/>
       <c r="E106" s="40"/>
@@ -7750,7 +6887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="3:37">
+    <row r="107" spans="3:37" ht="13.5" customHeight="1">
       <c r="C107" s="38"/>
       <c r="D107" s="39"/>
       <c r="E107" s="40"/>
@@ -7790,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="3:37">
+    <row r="108" spans="3:37" ht="13.5" customHeight="1">
       <c r="C108" s="38"/>
       <c r="D108" s="39"/>
       <c r="E108" s="40"/>
@@ -7830,7 +6967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="3:37">
+    <row r="109" spans="3:37" ht="13.5" customHeight="1">
       <c r="C109" s="38"/>
       <c r="D109" s="39"/>
       <c r="E109" s="40"/>
@@ -7870,7 +7007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="3:37">
+    <row r="110" spans="3:37" ht="13.5" customHeight="1">
       <c r="C110" s="38"/>
       <c r="D110" s="39"/>
       <c r="E110" s="40"/>
@@ -7910,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="3:37">
+    <row r="111" spans="3:37" ht="13.5" customHeight="1">
       <c r="C111" s="38"/>
       <c r="D111" s="39"/>
       <c r="E111" s="40"/>
@@ -7950,7 +7087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="3:37">
+    <row r="112" spans="3:37" ht="13.5" customHeight="1">
       <c r="C112" s="38"/>
       <c r="D112" s="39"/>
       <c r="E112" s="40"/>
@@ -7990,7 +7127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="3:37">
+    <row r="113" spans="3:37" ht="13.5" customHeight="1">
       <c r="C113" s="38"/>
       <c r="D113" s="39"/>
       <c r="E113" s="40"/>
@@ -8030,7 +7167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="3:37">
+    <row r="114" spans="3:37" ht="13.5" customHeight="1">
       <c r="C114" s="38"/>
       <c r="D114" s="39"/>
       <c r="E114" s="40"/>
@@ -8070,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="3:37">
+    <row r="115" spans="3:37" ht="13.5" customHeight="1">
       <c r="C115" s="38"/>
       <c r="D115" s="39"/>
       <c r="E115" s="40"/>
@@ -8110,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="3:37">
+    <row r="116" spans="3:37" ht="13.5" customHeight="1">
       <c r="C116" s="38"/>
       <c r="D116" s="39"/>
       <c r="E116" s="40"/>
@@ -8150,7 +7287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="3:37">
+    <row r="117" spans="3:37" ht="13.5" customHeight="1">
       <c r="C117" s="41"/>
       <c r="D117" s="42"/>
       <c r="E117" s="43"/>
@@ -8363,51 +7500,51 @@
       <c r="F121" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G121" s="85" t="s">
+      <c r="G121" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H121" s="85"/>
-      <c r="I121" s="85"/>
-      <c r="J121" s="85"/>
+      <c r="H121" s="98"/>
+      <c r="I121" s="98"/>
+      <c r="J121" s="98"/>
       <c r="K121" s="12"/>
       <c r="L121" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M121" s="86" t="s">
+      <c r="M121" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="N121" s="87"/>
-      <c r="O121" s="87"/>
-      <c r="P121" s="88"/>
+      <c r="N121" s="100"/>
+      <c r="O121" s="100"/>
+      <c r="P121" s="101"/>
       <c r="Q121" s="12"/>
       <c r="R121" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="S121" s="86" t="s">
+      <c r="S121" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="T121" s="87"/>
-      <c r="U121" s="87"/>
-      <c r="V121" s="88"/>
+      <c r="T121" s="100"/>
+      <c r="U121" s="100"/>
+      <c r="V121" s="101"/>
       <c r="X121" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="Y121" s="86" t="s">
+      <c r="Y121" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="Z121" s="87"/>
-      <c r="AA121" s="87"/>
-      <c r="AB121" s="88"/>
+      <c r="Z121" s="100"/>
+      <c r="AA121" s="100"/>
+      <c r="AB121" s="101"/>
       <c r="AC121" s="12"/>
       <c r="AD121" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="AE121" s="86" t="s">
+      <c r="AE121" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="AF121" s="87"/>
-      <c r="AG121" s="87"/>
-      <c r="AH121" s="88"/>
+      <c r="AF121" s="100"/>
+      <c r="AG121" s="100"/>
+      <c r="AH121" s="101"/>
     </row>
     <row r="122" spans="3:37" ht="3.75" customHeight="1">
       <c r="E122" s="13"/>
@@ -8417,49 +7554,49 @@
       <c r="F123" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G123" s="85" t="s">
+      <c r="G123" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="H123" s="85"/>
-      <c r="I123" s="85"/>
-      <c r="J123" s="85"/>
+      <c r="H123" s="98"/>
+      <c r="I123" s="98"/>
+      <c r="J123" s="98"/>
       <c r="L123" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="M123" s="85" t="s">
+      <c r="M123" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="N123" s="85"/>
-      <c r="O123" s="85"/>
-      <c r="P123" s="85"/>
+      <c r="N123" s="98"/>
+      <c r="O123" s="98"/>
+      <c r="P123" s="98"/>
       <c r="R123" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="S123" s="86" t="s">
+      <c r="S123" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="T123" s="87"/>
-      <c r="U123" s="87"/>
-      <c r="V123" s="88"/>
+      <c r="T123" s="100"/>
+      <c r="U123" s="100"/>
+      <c r="V123" s="101"/>
       <c r="W123" s="12"/>
       <c r="X123" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="Y123" s="86" t="s">
+      <c r="Y123" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="Z123" s="87"/>
-      <c r="AA123" s="87"/>
-      <c r="AB123" s="88"/>
+      <c r="Z123" s="100"/>
+      <c r="AA123" s="100"/>
+      <c r="AB123" s="101"/>
       <c r="AD123" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="AE123" s="89" t="s">
+      <c r="AE123" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="AF123" s="90"/>
-      <c r="AG123" s="90"/>
-      <c r="AH123" s="91"/>
+      <c r="AF123" s="103"/>
+      <c r="AG123" s="103"/>
+      <c r="AH123" s="104"/>
     </row>
     <row r="124" spans="3:37">
       <c r="E124" s="13"/>
@@ -8474,17 +7611,17 @@
       <c r="J125" s="71"/>
       <c r="K125" s="71"/>
       <c r="L125" s="71"/>
-      <c r="M125" s="72" t="s">
+      <c r="M125" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="N125" s="73"/>
-      <c r="O125" s="73"/>
-      <c r="P125" s="73"/>
-      <c r="Q125" s="73"/>
-      <c r="R125" s="73"/>
-      <c r="S125" s="73"/>
-      <c r="T125" s="73"/>
-      <c r="U125" s="74"/>
+      <c r="N125" s="86"/>
+      <c r="O125" s="86"/>
+      <c r="P125" s="86"/>
+      <c r="Q125" s="86"/>
+      <c r="R125" s="86"/>
+      <c r="S125" s="86"/>
+      <c r="T125" s="86"/>
+      <c r="U125" s="87"/>
       <c r="V125" s="71"/>
       <c r="W125" s="71"/>
       <c r="X125" s="71"/>
@@ -8508,15 +7645,15 @@
       <c r="J126" s="71"/>
       <c r="K126" s="71"/>
       <c r="L126" s="71"/>
-      <c r="M126" s="75"/>
-      <c r="N126" s="76"/>
-      <c r="O126" s="76"/>
-      <c r="P126" s="76"/>
-      <c r="Q126" s="76"/>
-      <c r="R126" s="76"/>
-      <c r="S126" s="76"/>
-      <c r="T126" s="76"/>
-      <c r="U126" s="77"/>
+      <c r="M126" s="88"/>
+      <c r="N126" s="89"/>
+      <c r="O126" s="89"/>
+      <c r="P126" s="89"/>
+      <c r="Q126" s="89"/>
+      <c r="R126" s="89"/>
+      <c r="S126" s="89"/>
+      <c r="T126" s="89"/>
+      <c r="U126" s="90"/>
       <c r="V126" s="71"/>
       <c r="W126" s="71"/>
       <c r="X126" s="71"/>
@@ -8540,15 +7677,15 @@
       <c r="J127" s="71"/>
       <c r="K127" s="71"/>
       <c r="L127" s="71"/>
-      <c r="M127" s="75"/>
-      <c r="N127" s="76"/>
-      <c r="O127" s="76"/>
-      <c r="P127" s="76"/>
-      <c r="Q127" s="76"/>
-      <c r="R127" s="76"/>
-      <c r="S127" s="76"/>
-      <c r="T127" s="76"/>
-      <c r="U127" s="77"/>
+      <c r="M127" s="88"/>
+      <c r="N127" s="89"/>
+      <c r="O127" s="89"/>
+      <c r="P127" s="89"/>
+      <c r="Q127" s="89"/>
+      <c r="R127" s="89"/>
+      <c r="S127" s="89"/>
+      <c r="T127" s="89"/>
+      <c r="U127" s="90"/>
       <c r="V127" s="71"/>
       <c r="W127" s="71"/>
       <c r="X127" s="71"/>
@@ -8572,15 +7709,15 @@
       <c r="J128" s="71"/>
       <c r="K128" s="71"/>
       <c r="L128" s="71"/>
-      <c r="M128" s="75"/>
-      <c r="N128" s="76"/>
-      <c r="O128" s="76"/>
-      <c r="P128" s="76"/>
-      <c r="Q128" s="76"/>
-      <c r="R128" s="76"/>
-      <c r="S128" s="76"/>
-      <c r="T128" s="76"/>
-      <c r="U128" s="77"/>
+      <c r="M128" s="88"/>
+      <c r="N128" s="89"/>
+      <c r="O128" s="89"/>
+      <c r="P128" s="89"/>
+      <c r="Q128" s="89"/>
+      <c r="R128" s="89"/>
+      <c r="S128" s="89"/>
+      <c r="T128" s="89"/>
+      <c r="U128" s="90"/>
       <c r="V128" s="71"/>
       <c r="W128" s="71"/>
       <c r="X128" s="71"/>
@@ -8605,15 +7742,15 @@
       <c r="J129" s="71"/>
       <c r="K129" s="71"/>
       <c r="L129" s="71"/>
-      <c r="M129" s="78"/>
-      <c r="N129" s="79"/>
-      <c r="O129" s="79"/>
-      <c r="P129" s="79"/>
-      <c r="Q129" s="79"/>
-      <c r="R129" s="79"/>
-      <c r="S129" s="79"/>
-      <c r="T129" s="79"/>
-      <c r="U129" s="80"/>
+      <c r="M129" s="91"/>
+      <c r="N129" s="92"/>
+      <c r="O129" s="92"/>
+      <c r="P129" s="92"/>
+      <c r="Q129" s="92"/>
+      <c r="R129" s="92"/>
+      <c r="S129" s="92"/>
+      <c r="T129" s="92"/>
+      <c r="U129" s="93"/>
       <c r="V129" s="71"/>
       <c r="W129" s="71"/>
       <c r="X129" s="71"/>
@@ -8664,12 +7801,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C6:AK7"/>
-    <mergeCell ref="C9:AK9"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="AK11:AK12"/>
     <mergeCell ref="M125:U125"/>
     <mergeCell ref="M126:U129"/>
     <mergeCell ref="C13:AK13"/>
@@ -8684,6 +7815,12 @@
     <mergeCell ref="S123:V123"/>
     <mergeCell ref="Y123:AB123"/>
     <mergeCell ref="AE123:AH123"/>
+    <mergeCell ref="C6:AK7"/>
+    <mergeCell ref="C9:AK9"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="AK11:AK12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F11:F117">

--- a/templates/fomio_template.xlsx
+++ b/templates/fomio_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geral\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481530AB-86EB-456E-B722-05699E49D0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{673CC24B-8B4D-4CEE-8135-905FD01CC6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F24CC36B-B49E-40ED-906B-853EB2E37C31}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F24CC36B-B49E-40ED-906B-853EB2E37C31}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -1459,36 +1459,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1549,11 +1519,3253 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="104">
+  <dxfs count="490">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2581,9 +5793,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2621,7 +5833,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2727,7 +5939,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2869,7 +6081,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2902,155 +6114,130 @@
     </row>
     <row r="5" spans="3:37"/>
     <row r="6" spans="3:37">
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="75"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="75"/>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75"/>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="75"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75"/>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75"/>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75"/>
-      <c r="W6" s="75"/>
-      <c r="X6" s="75"/>
-      <c r="Y6" s="75"/>
-      <c r="Z6" s="75"/>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="75"/>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="75"/>
-      <c r="AE6" s="75"/>
-      <c r="AF6" s="75"/>
-      <c r="AG6" s="75"/>
-      <c r="AH6" s="75"/>
-      <c r="AI6" s="75"/>
-      <c r="AJ6" s="75"/>
-      <c r="AK6" s="75"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="95"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="95"/>
+      <c r="J6" s="95"/>
+      <c r="K6" s="95"/>
+      <c r="L6" s="95"/>
+      <c r="M6" s="95"/>
+      <c r="N6" s="95"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="95"/>
+      <c r="Q6" s="95"/>
+      <c r="R6" s="95"/>
+      <c r="S6" s="95"/>
+      <c r="T6" s="95"/>
+      <c r="U6" s="95"/>
+      <c r="V6" s="95"/>
+      <c r="W6" s="95"/>
+      <c r="X6" s="95"/>
+      <c r="Y6" s="95"/>
+      <c r="Z6" s="95"/>
+      <c r="AA6" s="95"/>
+      <c r="AB6" s="95"/>
+      <c r="AC6" s="95"/>
+      <c r="AD6" s="95"/>
+      <c r="AE6" s="95"/>
+      <c r="AF6" s="95"/>
+      <c r="AG6" s="95"/>
+      <c r="AH6" s="95"/>
+      <c r="AI6" s="95"/>
+      <c r="AJ6" s="95"/>
+      <c r="AK6" s="95"/>
     </row>
     <row r="7" spans="3:37">
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
-      <c r="J7" s="75"/>
-      <c r="K7" s="75"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="75"/>
-      <c r="O7" s="75"/>
-      <c r="P7" s="75"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="75"/>
-      <c r="S7" s="75"/>
-      <c r="T7" s="75"/>
-      <c r="U7" s="75"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="75"/>
-      <c r="X7" s="75"/>
-      <c r="Y7" s="75"/>
-      <c r="Z7" s="75"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="75"/>
-      <c r="AC7" s="75"/>
-      <c r="AD7" s="75"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="75"/>
-      <c r="AH7" s="75"/>
-      <c r="AI7" s="75"/>
-      <c r="AJ7" s="75"/>
-      <c r="AK7" s="75"/>
-    </row>
-    <row r="8" spans="3:37" s="69" customFormat="1" ht="3.75" customHeight="1">
-      <c r="F8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Janeiro"&amp;" "&amp;YEAR(NOW()),C9="Maio"&amp;" "&amp;YEAR(NOW()),C9="Novembro"&amp;" "&amp;YEAR(NOW()),C9="Dezembro"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-      <c r="J8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Outubro"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-      <c r="M8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Dezembro"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-      <c r="O8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Junho"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-      <c r="T8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Agosto"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-      <c r="AD8" s="69" t="str">
-        <f ca="1">IF(OR(C9="Abril"&amp;" "&amp;YEAR(NOW()),C9="Dezembro"&amp;" "&amp;YEAR(NOW())),"FR","")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
+      <c r="H7" s="95"/>
+      <c r="I7" s="95"/>
+      <c r="J7" s="95"/>
+      <c r="K7" s="95"/>
+      <c r="L7" s="95"/>
+      <c r="M7" s="95"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="95"/>
+      <c r="P7" s="95"/>
+      <c r="Q7" s="95"/>
+      <c r="R7" s="95"/>
+      <c r="S7" s="95"/>
+      <c r="T7" s="95"/>
+      <c r="U7" s="95"/>
+      <c r="V7" s="95"/>
+      <c r="W7" s="95"/>
+      <c r="X7" s="95"/>
+      <c r="Y7" s="95"/>
+      <c r="Z7" s="95"/>
+      <c r="AA7" s="95"/>
+      <c r="AB7" s="95"/>
+      <c r="AC7" s="95"/>
+      <c r="AD7" s="95"/>
+      <c r="AE7" s="95"/>
+      <c r="AF7" s="95"/>
+      <c r="AG7" s="95"/>
+      <c r="AH7" s="95"/>
+      <c r="AI7" s="95"/>
+      <c r="AJ7" s="95"/>
+      <c r="AK7" s="95"/>
+    </row>
+    <row r="8" spans="3:37" s="69" customFormat="1" ht="3.75" customHeight="1"/>
     <row r="9" spans="3:37" ht="18.75">
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="76"/>
-      <c r="F9" s="76"/>
-      <c r="G9" s="76"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="76"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="76"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="76"/>
-      <c r="V9" s="76"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="76"/>
-      <c r="Y9" s="76"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="76"/>
-      <c r="AB9" s="76"/>
-      <c r="AC9" s="76"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="76"/>
-      <c r="AG9" s="76"/>
-      <c r="AH9" s="76"/>
-      <c r="AI9" s="76"/>
-      <c r="AJ9" s="76"/>
-      <c r="AK9" s="76"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="96"/>
+      <c r="R9" s="96"/>
+      <c r="S9" s="96"/>
+      <c r="T9" s="96"/>
+      <c r="U9" s="96"/>
+      <c r="V9" s="96"/>
+      <c r="W9" s="96"/>
+      <c r="X9" s="96"/>
+      <c r="Y9" s="96"/>
+      <c r="Z9" s="96"/>
+      <c r="AA9" s="96"/>
+      <c r="AB9" s="96"/>
+      <c r="AC9" s="96"/>
+      <c r="AD9" s="96"/>
+      <c r="AE9" s="96"/>
+      <c r="AF9" s="96"/>
+      <c r="AG9" s="96"/>
+      <c r="AH9" s="96"/>
+      <c r="AI9" s="96"/>
+      <c r="AJ9" s="96"/>
+      <c r="AK9" s="96"/>
     </row>
     <row r="10" spans="3:37" ht="3.75" customHeight="1">
       <c r="F10" s="70"/>
     </row>
     <row r="11" spans="3:37">
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="79" t="s">
+      <c r="D11" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="81" t="s">
+      <c r="E11" s="101" t="s">
         <v>4</v>
       </c>
       <c r="F11" s="61"/>
@@ -3084,14 +6271,14 @@
       <c r="AH11" s="61"/>
       <c r="AI11" s="61"/>
       <c r="AJ11" s="61"/>
-      <c r="AK11" s="83" t="s">
+      <c r="AK11" s="103" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="3:37">
-      <c r="C12" s="78"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="82"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="102"/>
       <c r="F12" s="62"/>
       <c r="G12" s="63"/>
       <c r="H12" s="63"/>
@@ -3123,46 +6310,46 @@
       <c r="AH12" s="63"/>
       <c r="AI12" s="63"/>
       <c r="AJ12" s="64"/>
-      <c r="AK12" s="84"/>
+      <c r="AK12" s="104"/>
     </row>
     <row r="13" spans="3:37">
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="84" t="s">
         <v>6</v>
       </c>
-      <c r="D13" s="95"/>
-      <c r="E13" s="95"/>
-      <c r="F13" s="95"/>
-      <c r="G13" s="95"/>
-      <c r="H13" s="95"/>
-      <c r="I13" s="95"/>
-      <c r="J13" s="95"/>
-      <c r="K13" s="95"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="95"/>
-      <c r="N13" s="95"/>
-      <c r="O13" s="95"/>
-      <c r="P13" s="95"/>
-      <c r="Q13" s="95"/>
-      <c r="R13" s="95"/>
-      <c r="S13" s="95"/>
-      <c r="T13" s="95"/>
-      <c r="U13" s="95"/>
-      <c r="V13" s="95"/>
-      <c r="W13" s="95"/>
-      <c r="X13" s="95"/>
-      <c r="Y13" s="95"/>
-      <c r="Z13" s="95"/>
-      <c r="AA13" s="95"/>
-      <c r="AB13" s="95"/>
-      <c r="AC13" s="95"/>
-      <c r="AD13" s="95"/>
-      <c r="AE13" s="95"/>
-      <c r="AF13" s="95"/>
-      <c r="AG13" s="95"/>
-      <c r="AH13" s="95"/>
-      <c r="AI13" s="95"/>
-      <c r="AJ13" s="95"/>
-      <c r="AK13" s="96"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="85"/>
+      <c r="J13" s="85"/>
+      <c r="K13" s="85"/>
+      <c r="L13" s="85"/>
+      <c r="M13" s="85"/>
+      <c r="N13" s="85"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="85"/>
+      <c r="R13" s="85"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="85"/>
+      <c r="U13" s="85"/>
+      <c r="V13" s="85"/>
+      <c r="W13" s="85"/>
+      <c r="X13" s="85"/>
+      <c r="Y13" s="85"/>
+      <c r="Z13" s="85"/>
+      <c r="AA13" s="85"/>
+      <c r="AB13" s="85"/>
+      <c r="AC13" s="85"/>
+      <c r="AD13" s="85"/>
+      <c r="AE13" s="85"/>
+      <c r="AF13" s="85"/>
+      <c r="AG13" s="85"/>
+      <c r="AH13" s="85"/>
+      <c r="AI13" s="85"/>
+      <c r="AJ13" s="85"/>
+      <c r="AK13" s="86"/>
     </row>
     <row r="14" spans="3:37" ht="13.5" customHeight="1">
       <c r="C14" s="72"/>
@@ -3285,43 +6472,43 @@
       </c>
     </row>
     <row r="17" spans="3:38">
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="95"/>
-      <c r="E17" s="95"/>
-      <c r="F17" s="95"/>
-      <c r="G17" s="95"/>
-      <c r="H17" s="97"/>
-      <c r="I17" s="97"/>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="97"/>
-      <c r="N17" s="97"/>
-      <c r="O17" s="97"/>
-      <c r="P17" s="97"/>
-      <c r="Q17" s="97"/>
-      <c r="R17" s="97"/>
-      <c r="S17" s="97"/>
-      <c r="T17" s="97"/>
-      <c r="U17" s="97"/>
-      <c r="V17" s="97"/>
-      <c r="W17" s="97"/>
-      <c r="X17" s="97"/>
-      <c r="Y17" s="97"/>
-      <c r="Z17" s="97"/>
-      <c r="AA17" s="97"/>
-      <c r="AB17" s="97"/>
-      <c r="AC17" s="97"/>
-      <c r="AD17" s="97"/>
-      <c r="AE17" s="97"/>
-      <c r="AF17" s="97"/>
-      <c r="AG17" s="97"/>
-      <c r="AH17" s="97"/>
-      <c r="AI17" s="97"/>
-      <c r="AJ17" s="97"/>
-      <c r="AK17" s="96"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+      <c r="J17" s="87"/>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="87"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="87"/>
+      <c r="R17" s="87"/>
+      <c r="S17" s="87"/>
+      <c r="T17" s="87"/>
+      <c r="U17" s="87"/>
+      <c r="V17" s="87"/>
+      <c r="W17" s="87"/>
+      <c r="X17" s="87"/>
+      <c r="Y17" s="87"/>
+      <c r="Z17" s="87"/>
+      <c r="AA17" s="87"/>
+      <c r="AB17" s="87"/>
+      <c r="AC17" s="87"/>
+      <c r="AD17" s="87"/>
+      <c r="AE17" s="87"/>
+      <c r="AF17" s="87"/>
+      <c r="AG17" s="87"/>
+      <c r="AH17" s="87"/>
+      <c r="AI17" s="87"/>
+      <c r="AJ17" s="87"/>
+      <c r="AK17" s="86"/>
     </row>
     <row r="18" spans="3:38" ht="13.5" customHeight="1">
       <c r="C18" s="55"/>
@@ -7500,51 +10687,51 @@
       <c r="F121" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G121" s="98" t="s">
+      <c r="G121" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="H121" s="98"/>
-      <c r="I121" s="98"/>
-      <c r="J121" s="98"/>
+      <c r="H121" s="88"/>
+      <c r="I121" s="88"/>
+      <c r="J121" s="88"/>
       <c r="K121" s="12"/>
       <c r="L121" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="M121" s="99" t="s">
+      <c r="M121" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="N121" s="100"/>
-      <c r="O121" s="100"/>
-      <c r="P121" s="101"/>
+      <c r="N121" s="90"/>
+      <c r="O121" s="90"/>
+      <c r="P121" s="91"/>
       <c r="Q121" s="12"/>
       <c r="R121" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="S121" s="99" t="s">
+      <c r="S121" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="T121" s="100"/>
-      <c r="U121" s="100"/>
-      <c r="V121" s="101"/>
+      <c r="T121" s="90"/>
+      <c r="U121" s="90"/>
+      <c r="V121" s="91"/>
       <c r="X121" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="Y121" s="99" t="s">
+      <c r="Y121" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="Z121" s="100"/>
-      <c r="AA121" s="100"/>
-      <c r="AB121" s="101"/>
+      <c r="Z121" s="90"/>
+      <c r="AA121" s="90"/>
+      <c r="AB121" s="91"/>
       <c r="AC121" s="12"/>
       <c r="AD121" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="AE121" s="99" t="s">
+      <c r="AE121" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="AF121" s="100"/>
-      <c r="AG121" s="100"/>
-      <c r="AH121" s="101"/>
+      <c r="AF121" s="90"/>
+      <c r="AG121" s="90"/>
+      <c r="AH121" s="91"/>
     </row>
     <row r="122" spans="3:37" ht="3.75" customHeight="1">
       <c r="E122" s="13"/>
@@ -7554,49 +10741,49 @@
       <c r="F123" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G123" s="98" t="s">
+      <c r="G123" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="H123" s="98"/>
-      <c r="I123" s="98"/>
-      <c r="J123" s="98"/>
+      <c r="H123" s="88"/>
+      <c r="I123" s="88"/>
+      <c r="J123" s="88"/>
       <c r="L123" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="M123" s="98" t="s">
+      <c r="M123" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="N123" s="98"/>
-      <c r="O123" s="98"/>
-      <c r="P123" s="98"/>
+      <c r="N123" s="88"/>
+      <c r="O123" s="88"/>
+      <c r="P123" s="88"/>
       <c r="R123" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="S123" s="99" t="s">
+      <c r="S123" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="T123" s="100"/>
-      <c r="U123" s="100"/>
-      <c r="V123" s="101"/>
+      <c r="T123" s="90"/>
+      <c r="U123" s="90"/>
+      <c r="V123" s="91"/>
       <c r="W123" s="12"/>
       <c r="X123" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="Y123" s="99" t="s">
+      <c r="Y123" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="Z123" s="100"/>
-      <c r="AA123" s="100"/>
-      <c r="AB123" s="101"/>
+      <c r="Z123" s="90"/>
+      <c r="AA123" s="90"/>
+      <c r="AB123" s="91"/>
       <c r="AD123" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="AE123" s="102" t="s">
+      <c r="AE123" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="AF123" s="103"/>
-      <c r="AG123" s="103"/>
-      <c r="AH123" s="104"/>
+      <c r="AF123" s="93"/>
+      <c r="AG123" s="93"/>
+      <c r="AH123" s="94"/>
     </row>
     <row r="124" spans="3:37">
       <c r="E124" s="13"/>
@@ -7611,17 +10798,17 @@
       <c r="J125" s="71"/>
       <c r="K125" s="71"/>
       <c r="L125" s="71"/>
-      <c r="M125" s="85" t="s">
+      <c r="M125" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="N125" s="86"/>
-      <c r="O125" s="86"/>
-      <c r="P125" s="86"/>
-      <c r="Q125" s="86"/>
-      <c r="R125" s="86"/>
-      <c r="S125" s="86"/>
-      <c r="T125" s="86"/>
-      <c r="U125" s="87"/>
+      <c r="N125" s="76"/>
+      <c r="O125" s="76"/>
+      <c r="P125" s="76"/>
+      <c r="Q125" s="76"/>
+      <c r="R125" s="76"/>
+      <c r="S125" s="76"/>
+      <c r="T125" s="76"/>
+      <c r="U125" s="77"/>
       <c r="V125" s="71"/>
       <c r="W125" s="71"/>
       <c r="X125" s="71"/>
@@ -7645,15 +10832,15 @@
       <c r="J126" s="71"/>
       <c r="K126" s="71"/>
       <c r="L126" s="71"/>
-      <c r="M126" s="88"/>
-      <c r="N126" s="89"/>
-      <c r="O126" s="89"/>
-      <c r="P126" s="89"/>
-      <c r="Q126" s="89"/>
-      <c r="R126" s="89"/>
-      <c r="S126" s="89"/>
-      <c r="T126" s="89"/>
-      <c r="U126" s="90"/>
+      <c r="M126" s="78"/>
+      <c r="N126" s="79"/>
+      <c r="O126" s="79"/>
+      <c r="P126" s="79"/>
+      <c r="Q126" s="79"/>
+      <c r="R126" s="79"/>
+      <c r="S126" s="79"/>
+      <c r="T126" s="79"/>
+      <c r="U126" s="80"/>
       <c r="V126" s="71"/>
       <c r="W126" s="71"/>
       <c r="X126" s="71"/>
@@ -7677,15 +10864,15 @@
       <c r="J127" s="71"/>
       <c r="K127" s="71"/>
       <c r="L127" s="71"/>
-      <c r="M127" s="88"/>
-      <c r="N127" s="89"/>
-      <c r="O127" s="89"/>
-      <c r="P127" s="89"/>
-      <c r="Q127" s="89"/>
-      <c r="R127" s="89"/>
-      <c r="S127" s="89"/>
-      <c r="T127" s="89"/>
-      <c r="U127" s="90"/>
+      <c r="M127" s="78"/>
+      <c r="N127" s="79"/>
+      <c r="O127" s="79"/>
+      <c r="P127" s="79"/>
+      <c r="Q127" s="79"/>
+      <c r="R127" s="79"/>
+      <c r="S127" s="79"/>
+      <c r="T127" s="79"/>
+      <c r="U127" s="80"/>
       <c r="V127" s="71"/>
       <c r="W127" s="71"/>
       <c r="X127" s="71"/>
@@ -7709,15 +10896,15 @@
       <c r="J128" s="71"/>
       <c r="K128" s="71"/>
       <c r="L128" s="71"/>
-      <c r="M128" s="88"/>
-      <c r="N128" s="89"/>
-      <c r="O128" s="89"/>
-      <c r="P128" s="89"/>
-      <c r="Q128" s="89"/>
-      <c r="R128" s="89"/>
-      <c r="S128" s="89"/>
-      <c r="T128" s="89"/>
-      <c r="U128" s="90"/>
+      <c r="M128" s="78"/>
+      <c r="N128" s="79"/>
+      <c r="O128" s="79"/>
+      <c r="P128" s="79"/>
+      <c r="Q128" s="79"/>
+      <c r="R128" s="79"/>
+      <c r="S128" s="79"/>
+      <c r="T128" s="79"/>
+      <c r="U128" s="80"/>
       <c r="V128" s="71"/>
       <c r="W128" s="71"/>
       <c r="X128" s="71"/>
@@ -7742,15 +10929,15 @@
       <c r="J129" s="71"/>
       <c r="K129" s="71"/>
       <c r="L129" s="71"/>
-      <c r="M129" s="91"/>
-      <c r="N129" s="92"/>
-      <c r="O129" s="92"/>
-      <c r="P129" s="92"/>
-      <c r="Q129" s="92"/>
-      <c r="R129" s="92"/>
-      <c r="S129" s="92"/>
-      <c r="T129" s="92"/>
-      <c r="U129" s="93"/>
+      <c r="M129" s="81"/>
+      <c r="N129" s="82"/>
+      <c r="O129" s="82"/>
+      <c r="P129" s="82"/>
+      <c r="Q129" s="82"/>
+      <c r="R129" s="82"/>
+      <c r="S129" s="82"/>
+      <c r="T129" s="82"/>
+      <c r="U129" s="83"/>
       <c r="V129" s="71"/>
       <c r="W129" s="71"/>
       <c r="X129" s="71"/>
@@ -7801,6 +10988,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:AK7"/>
+    <mergeCell ref="C9:AK9"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="AK11:AK12"/>
     <mergeCell ref="M125:U125"/>
     <mergeCell ref="M126:U129"/>
     <mergeCell ref="C13:AK13"/>
@@ -7815,389 +11008,339 @@
     <mergeCell ref="S123:V123"/>
     <mergeCell ref="Y123:AB123"/>
     <mergeCell ref="AE123:AH123"/>
-    <mergeCell ref="C6:AK7"/>
-    <mergeCell ref="C9:AK9"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="AK11:AK12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="F11:F117">
-    <cfRule type="expression" dxfId="103" priority="169">
-      <formula>$F$11="SÁB"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="102" priority="168">
-      <formula>$F$8="FR"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="101" priority="170">
-      <formula>$F$11="DOM"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F14:AJ16">
-    <cfRule type="cellIs" dxfId="100" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="5" operator="equal">
       <formula>"N"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:AJ117">
-    <cfRule type="cellIs" dxfId="99" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="2" operator="equal">
       <formula>"ET"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="3" operator="equal">
       <formula>"EN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="4" operator="equal">
       <formula>"ED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="6" operator="equal">
       <formula>"PN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="7" operator="equal">
       <formula>"PD"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="8" operator="equal">
       <formula>"PT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="9" operator="equal">
       <formula>"FO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="10" operator="equal">
       <formula>"FE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="11" operator="equal">
       <formula>"BX"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="1" operator="equal">
       <formula>"EP"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G117">
-    <cfRule type="expression" dxfId="89" priority="165">
-      <formula>$G$8="FR"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="88" priority="166">
-      <formula>$G$11="SÁB"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="87" priority="167">
-      <formula>$G$11="DOM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11:H117">
-    <cfRule type="expression" dxfId="86" priority="163">
-      <formula>$H$11="SÁB"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="162">
-      <formula>$H$8="FR"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="164">
-      <formula>$H$11="DOM"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I117">
-    <cfRule type="expression" dxfId="83" priority="159">
-      <formula>$I$8="FR"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="161">
-      <formula>$I$11="DOM"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="160">
-      <formula>$I$11="SÁB"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J11:J117">
-    <cfRule type="expression" dxfId="80" priority="158">
+    <cfRule type="expression" dxfId="175" priority="158">
       <formula>$J$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="156">
+    <cfRule type="expression" dxfId="174" priority="156">
       <formula>$J$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="157">
+    <cfRule type="expression" dxfId="173" priority="157">
       <formula>$J$11="SÁB"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:K117">
-    <cfRule type="expression" dxfId="77" priority="155">
+    <cfRule type="expression" dxfId="172" priority="155">
       <formula>$K$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="153">
+    <cfRule type="expression" dxfId="171" priority="153">
       <formula>$K$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="154">
+    <cfRule type="expression" dxfId="170" priority="154">
       <formula>$K$11="SÁB"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L11:L117">
-    <cfRule type="expression" dxfId="74" priority="151">
+    <cfRule type="expression" dxfId="169" priority="151">
       <formula>$L$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="150">
+    <cfRule type="expression" dxfId="168" priority="150">
       <formula>$L$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="152">
+    <cfRule type="expression" dxfId="167" priority="152">
       <formula>$L$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M11:M117">
-    <cfRule type="expression" dxfId="71" priority="149">
+    <cfRule type="expression" dxfId="166" priority="149">
       <formula>$M$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="148">
+    <cfRule type="expression" dxfId="165" priority="148">
       <formula>$M$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="147">
+    <cfRule type="expression" dxfId="164" priority="147">
       <formula>$M$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N11:N117">
-    <cfRule type="expression" dxfId="68" priority="146">
+    <cfRule type="expression" dxfId="163" priority="146">
       <formula>$N$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="145">
+    <cfRule type="expression" dxfId="162" priority="145">
       <formula>$N$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="144">
+    <cfRule type="expression" dxfId="161" priority="144">
       <formula>$N$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11:O117">
-    <cfRule type="expression" dxfId="65" priority="141">
+    <cfRule type="expression" dxfId="160" priority="141">
       <formula>$O$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="142">
+    <cfRule type="expression" dxfId="159" priority="142">
       <formula>$O$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="143">
+    <cfRule type="expression" dxfId="158" priority="143">
       <formula>$O$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P117">
-    <cfRule type="expression" dxfId="62" priority="139">
+    <cfRule type="expression" dxfId="157" priority="139">
       <formula>$P$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="140">
+    <cfRule type="expression" dxfId="156" priority="140">
       <formula>$P$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="138">
+    <cfRule type="expression" dxfId="155" priority="138">
       <formula>$P$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q11:Q117">
-    <cfRule type="expression" dxfId="59" priority="137">
+    <cfRule type="expression" dxfId="154" priority="137">
       <formula>$Q$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="73">
+    <cfRule type="expression" dxfId="153" priority="73">
       <formula>$Q$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="72">
+    <cfRule type="expression" dxfId="152" priority="72">
       <formula>$Q$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R11:R117">
-    <cfRule type="expression" dxfId="56" priority="66">
+    <cfRule type="expression" dxfId="151" priority="66">
       <formula>$R$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="71">
+    <cfRule type="expression" dxfId="150" priority="71">
       <formula>$R$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="67">
+    <cfRule type="expression" dxfId="149" priority="67">
       <formula>$R$11="SÁB"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S11:S117">
-    <cfRule type="expression" dxfId="53" priority="64">
+    <cfRule type="expression" dxfId="148" priority="64">
       <formula>$S$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="63">
+    <cfRule type="expression" dxfId="147" priority="63">
       <formula>$S$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="65">
+    <cfRule type="expression" dxfId="146" priority="65">
       <formula>$S$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T11:T117">
-    <cfRule type="expression" dxfId="50" priority="62">
+    <cfRule type="expression" dxfId="145" priority="62">
       <formula>$T$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="61">
+    <cfRule type="expression" dxfId="144" priority="61">
       <formula>$T$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="60">
+    <cfRule type="expression" dxfId="143" priority="60">
       <formula>$T$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U11:U117">
-    <cfRule type="expression" dxfId="47" priority="59">
+    <cfRule type="expression" dxfId="142" priority="59">
       <formula>$U$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="58">
+    <cfRule type="expression" dxfId="141" priority="58">
       <formula>$U$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="57">
+    <cfRule type="expression" dxfId="140" priority="57">
       <formula>$U$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V11:V117">
-    <cfRule type="expression" dxfId="44" priority="55">
+    <cfRule type="expression" dxfId="139" priority="55">
       <formula>$V$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="54">
+    <cfRule type="expression" dxfId="138" priority="54">
       <formula>$V$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="56">
+    <cfRule type="expression" dxfId="137" priority="56">
       <formula>$V$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W11:W117">
-    <cfRule type="expression" dxfId="41" priority="51">
+    <cfRule type="expression" dxfId="136" priority="51">
       <formula>$W$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="52">
+    <cfRule type="expression" dxfId="135" priority="52">
       <formula>$W$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="53">
+    <cfRule type="expression" dxfId="134" priority="53">
       <formula>$W$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X11:X117">
-    <cfRule type="expression" dxfId="38" priority="48">
+    <cfRule type="expression" dxfId="133" priority="48">
       <formula>$X$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="49">
+    <cfRule type="expression" dxfId="132" priority="49">
       <formula>$X$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="50">
+    <cfRule type="expression" dxfId="131" priority="50">
       <formula>$X$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y11:Y117">
-    <cfRule type="expression" dxfId="35" priority="45">
+    <cfRule type="expression" dxfId="130" priority="45">
       <formula>$Y$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="46">
+    <cfRule type="expression" dxfId="129" priority="46">
       <formula>$Y$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="47">
+    <cfRule type="expression" dxfId="128" priority="47">
       <formula>$Y$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z11:Z117">
-    <cfRule type="expression" dxfId="32" priority="44">
+    <cfRule type="expression" dxfId="127" priority="44">
       <formula>$Z$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="42">
+    <cfRule type="expression" dxfId="126" priority="42">
       <formula>$Z$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="43">
+    <cfRule type="expression" dxfId="125" priority="43">
       <formula>$Z$11="SÁB"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA11:AA117">
-    <cfRule type="expression" dxfId="29" priority="40">
+    <cfRule type="expression" dxfId="124" priority="40">
       <formula>$AA$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="39">
+    <cfRule type="expression" dxfId="123" priority="39">
       <formula>$AA$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="41">
+    <cfRule type="expression" dxfId="122" priority="41">
       <formula>$AA$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB11:AB117">
-    <cfRule type="expression" dxfId="26" priority="37">
+    <cfRule type="expression" dxfId="121" priority="37">
       <formula>$AB$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="36">
+    <cfRule type="expression" dxfId="120" priority="36">
       <formula>$AB$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="38">
+    <cfRule type="expression" dxfId="119" priority="38">
       <formula>$AB$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC117">
-    <cfRule type="expression" dxfId="23" priority="35">
+    <cfRule type="expression" dxfId="118" priority="35">
       <formula>$AC$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="34">
+    <cfRule type="expression" dxfId="117" priority="34">
       <formula>$AC$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="33">
+    <cfRule type="expression" dxfId="116" priority="33">
       <formula>$AC$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD117">
-    <cfRule type="expression" dxfId="20" priority="32">
+    <cfRule type="expression" dxfId="115" priority="32">
       <formula>$AD$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="31">
+    <cfRule type="expression" dxfId="114" priority="31">
       <formula>$AD$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="30">
+    <cfRule type="expression" dxfId="113" priority="30">
       <formula>$AD$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE11:AE117">
-    <cfRule type="expression" dxfId="17" priority="27">
+    <cfRule type="expression" dxfId="112" priority="27">
       <formula>$AE$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="28">
+    <cfRule type="expression" dxfId="111" priority="28">
       <formula>$AE$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="29">
+    <cfRule type="expression" dxfId="110" priority="29">
       <formula>$AE$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF11:AF117">
-    <cfRule type="expression" dxfId="14" priority="24">
+    <cfRule type="expression" dxfId="109" priority="24">
       <formula>$AF$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="25">
+    <cfRule type="expression" dxfId="108" priority="25">
       <formula>$AF$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="26">
+    <cfRule type="expression" dxfId="107" priority="26">
       <formula>$AF$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG11:AG117">
-    <cfRule type="expression" dxfId="11" priority="21">
+    <cfRule type="expression" dxfId="106" priority="21">
       <formula>$AG$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="22">
+    <cfRule type="expression" dxfId="105" priority="22">
       <formula>$AG$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="23">
+    <cfRule type="expression" dxfId="104" priority="23">
       <formula>$AG$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH11:AH117">
-    <cfRule type="expression" dxfId="8" priority="18">
+    <cfRule type="expression" dxfId="103" priority="18">
       <formula>$AH$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="20">
+    <cfRule type="expression" dxfId="102" priority="20">
       <formula>$AH$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="19">
+    <cfRule type="expression" dxfId="101" priority="19">
       <formula>$AH$11="SÁB"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI11:AI117">
-    <cfRule type="expression" dxfId="5" priority="17">
+    <cfRule type="expression" dxfId="100" priority="17">
       <formula>$AI$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="16">
+    <cfRule type="expression" dxfId="99" priority="16">
       <formula>$AI$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="15">
+    <cfRule type="expression" dxfId="98" priority="15">
       <formula>$AI$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ11:AJ117">
-    <cfRule type="expression" dxfId="2" priority="13">
+    <cfRule type="expression" dxfId="97" priority="13">
       <formula>$AJ$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="12">
+    <cfRule type="expression" dxfId="96" priority="12">
       <formula>$AJ$8="FR"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="95" priority="14">
       <formula>$AJ$11="DOM"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/templates/fomio_template.xlsx
+++ b/templates/fomio_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2E4612-2862-462F-A70B-42B76EF123B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D51C384-A469-4C28-ABB1-867F3425722A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F24CC36B-B49E-40ED-906B-853EB2E37C31}"/>
   </bookViews>
@@ -1550,7 +1550,1087 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8301">
+  <dxfs count="8436">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF002060"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC0CB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF90EE90"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -73432,16 +74512,16 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F11:F117">
-    <cfRule type="expression" dxfId="269" priority="118">
+    <cfRule type="expression" dxfId="269" priority="285">
       <formula>$F$8="CA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="268" priority="117">
+    <cfRule type="expression" dxfId="268" priority="284">
       <formula>$F$11="DOM"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="267" priority="116">
+    <cfRule type="expression" dxfId="267" priority="283">
       <formula>$F$11="SÁB"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="266" priority="119">
+    <cfRule type="expression" dxfId="266" priority="286">
       <formula>$F$8="FR"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -73451,34 +74531,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:AJ117">
-    <cfRule type="cellIs" dxfId="264" priority="126" operator="equal">
+    <cfRule type="cellIs" dxfId="264" priority="116" operator="equal">
       <formula>"ET"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="263" priority="286" operator="equal">
+    <cfRule type="cellIs" dxfId="263" priority="282" operator="equal">
       <formula>"EP"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="282" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="127" operator="equal">
       <formula>"PT"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="261" priority="283" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="278" operator="equal">
       <formula>"FO"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="260" priority="284" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="279" operator="equal">
       <formula>"FE"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="285" operator="equal">
+    <cfRule type="cellIs" dxfId="259" priority="281" operator="equal">
       <formula>"BX"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="258" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="117" operator="equal">
       <formula>"EN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="257" priority="278" operator="equal">
+    <cfRule type="cellIs" dxfId="257" priority="118" operator="equal">
       <formula>"ED"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="279" operator="equal">
+    <cfRule type="cellIs" dxfId="256" priority="119" operator="equal">
       <formula>"PN"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="281" operator="equal">
+    <cfRule type="cellIs" dxfId="255" priority="126" operator="equal">
       <formula>"PD"</formula>
     </cfRule>
   </conditionalFormatting>
